--- a/Packages/cn.etetet.yiuiluban/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuiluban/Luban/Config/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="13890"/>
+    <workbookView windowWidth="21863" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="YIUI" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -114,12 +114,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>yiuilubangen</t>
-  </si>
-  <si>
-    <t>Demo</t>
   </si>
 </sst>
 </file>
@@ -804,13 +798,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,18 +1058,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="13.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="3" width="29.375" customWidth="1"/>
+    <col min="2" max="3" width="29.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="51.5" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
-    <col min="6" max="6" width="27.875" customWidth="1"/>
-    <col min="7" max="7" width="82.375" customWidth="1"/>
+    <col min="5" max="5" width="32.6296296296296" customWidth="1"/>
+    <col min="6" max="6" width="27.8796296296296" customWidth="1"/>
+    <col min="7" max="7" width="82.3796296296296" customWidth="1"/>
     <col min="8" max="11" width="16.5" customWidth="1"/>
-    <col min="12" max="12" width="25.625" customWidth="1"/>
-    <col min="13" max="13" width="49.875" customWidth="1"/>
+    <col min="12" max="12" width="25.6296296296296" customWidth="1"/>
+    <col min="13" max="13" width="49.8796296296296" customWidth="1"/>
     <col min="14" max="16384" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1186,36 +1173,6 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:13">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
-        <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
-      </c>
-      <c r="E4" t="str">
-        <f>_xlfn.CONCAT(C4,"Config")</f>
-        <v>DemoConfig</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
-        <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
-      </c>
-      <c r="M4" t="str">
-        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
-        <v>DemoConfigCategory</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Packages/cn.etetet.yiuiluban/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuiluban/Luban/Config/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21863" windowHeight="12180"/>
+    <workbookView windowWidth="25185" windowHeight="13890"/>
   </bookViews>
   <sheets>
     <sheet name="YIUI" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>yiuilubangen</t>
+  </si>
+  <si>
+    <t>Demo</t>
   </si>
 </sst>
 </file>
@@ -798,6 +804,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1058,18 +1071,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="13.8" outlineLevelRow="2"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="3" width="29.3796296296296" customWidth="1"/>
+    <col min="2" max="3" width="29.375" customWidth="1"/>
     <col min="4" max="4" width="51.5" customWidth="1"/>
-    <col min="5" max="5" width="32.6296296296296" customWidth="1"/>
-    <col min="6" max="6" width="27.8796296296296" customWidth="1"/>
-    <col min="7" max="7" width="82.3796296296296" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="27.875" customWidth="1"/>
+    <col min="7" max="7" width="82.375" customWidth="1"/>
     <col min="8" max="11" width="16.5" customWidth="1"/>
-    <col min="12" max="12" width="25.6296296296296" customWidth="1"/>
-    <col min="13" max="13" width="49.8796296296296" customWidth="1"/>
+    <col min="12" max="12" width="25.625" customWidth="1"/>
+    <col min="13" max="13" width="49.875" customWidth="1"/>
     <col min="14" max="16384" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1173,6 +1186,36 @@
         <v>28</v>
       </c>
     </row>
+    <row r="4" customFormat="1" spans="1:13">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="str">
+        <f>_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
+        <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
+      </c>
+      <c r="E4" t="str">
+        <f>_xlfn.CONCAT(C4,"Config")</f>
+        <v>DemoConfig</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
+      </c>
+      <c r="M4" t="str">
+        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <v>DemoConfigCategory</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
